--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Categories" sheetId="1" state="visible" r:id="rId3"/>

--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="1030">
   <si>
     <t>Id</t>
   </si>
@@ -2656,6 +2656,42 @@
   </si>
   <si>
     <t>0.5 MB</t>
+  </si>
+  <si>
+    <t>pl4</t>
+  </si>
+  <si>
+    <t>Automated Pricelist (2020)</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>Jul 2023</t>
+  </si>
+  <si>
+    <t>3.2 MB</t>
+  </si>
+  <si>
+    <t>pl5</t>
+  </si>
+  <si>
+    <t>Flo-Tite General Price Guide (2023)</t>
+  </si>
+  <si>
+    <t>Dec 2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Aug 2026</t>
+  </si>
+  <si>
+    <t>8.0 MB</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/Flo-Tite 2023 FINAL General Price Guide_12_20_2022 COMPRESSED.pdf</t>
   </si>
   <si>
     <t>Desc</t>
@@ -4230,7 +4266,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="8.01" style="1" customWidth="1"/>
@@ -4242,7 +4278,7 @@
     <col min="7" max="8" width="12.01" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4266,6 +4302,9 @@
       </c>
       <c r="H1" s="4" t="s">
         <v>725</v>
+      </c>
+      <c r="I1" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4344,6 +4383,64 @@
       </c>
       <c r="H4" s="6" t="s">
         <v>872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="I5" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="I6" t="s">
+        <v>884</v>
       </c>
     </row>
   </sheetData>
@@ -4382,28 +4479,28 @@
         <v>438</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>726</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>724</v>
@@ -4420,25 +4517,25 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>730</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>32</v>
@@ -4446,22 +4543,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>739</v>
@@ -4469,25 +4566,25 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>864</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -4514,7 +4611,7 @@
         <v>436</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -5434,45 +5531,45 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>905</v>
+        <v>917</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>121</v>
@@ -5480,22 +5577,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>913</v>
+        <v>925</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>138</v>
@@ -5503,22 +5600,22 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>916</v>
+        <v>928</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>151</v>
@@ -5526,22 +5623,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>921</v>
+        <v>933</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>161</v>
@@ -5549,22 +5646,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>924</v>
+        <v>936</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>174</v>
@@ -5572,22 +5669,22 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>188</v>
@@ -5595,22 +5692,22 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>197</v>
@@ -5618,22 +5715,22 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>635</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>633</v>
@@ -5641,22 +5738,22 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>639</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>939</v>
+        <v>951</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>637</v>
@@ -5664,22 +5761,22 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>941</v>
+        <v>953</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>643</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>942</v>
+        <v>954</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>641</v>
@@ -5687,22 +5784,22 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>943</v>
+        <v>955</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>647</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>645</v>
@@ -5710,22 +5807,22 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>651</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>948</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>936</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>649</v>
@@ -5733,22 +5830,22 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>949</v>
+        <v>961</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>950</v>
+        <v>962</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>655</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>951</v>
+        <v>963</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>653</v>
@@ -5756,22 +5853,22 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>952</v>
+        <v>964</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>659</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>954</v>
+        <v>966</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>657</v>
@@ -5779,22 +5876,22 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>663</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>661</v>
@@ -5802,22 +5899,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>667</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>665</v>
@@ -5825,22 +5922,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>671</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>669</v>
@@ -5848,22 +5945,22 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>675</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>673</v>
@@ -5871,22 +5968,22 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>679</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>677</v>
@@ -5894,22 +5991,22 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>970</v>
+        <v>982</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>683</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>972</v>
+        <v>984</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>681</v>
@@ -5917,45 +6014,45 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>735</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>729</v>
@@ -5963,22 +6060,22 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>736</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>729</v>
@@ -6026,7 +6123,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6040,7 +6137,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -6054,7 +6151,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -6068,7 +6165,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -6082,7 +6179,7 @@
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -6096,7 +6193,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -6110,7 +6207,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -6124,7 +6221,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -6138,7 +6235,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -6152,7 +6249,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -6166,7 +6263,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -6180,7 +6277,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -6194,7 +6291,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -6208,7 +6305,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -6222,7 +6319,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -6236,7 +6333,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -6250,7 +6347,7 @@
         <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -6264,7 +6361,7 @@
         <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -6278,7 +6375,7 @@
         <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -6292,7 +6389,7 @@
         <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -6306,7 +6403,7 @@
         <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -6320,7 +6417,7 @@
         <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -6334,7 +6431,7 @@
         <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
@@ -6348,7 +6445,7 @@
         <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -6362,7 +6459,7 @@
         <v>228</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -6376,7 +6473,7 @@
         <v>228</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -6390,7 +6487,7 @@
         <v>228</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -6404,7 +6501,7 @@
         <v>238</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -6418,7 +6515,7 @@
         <v>238</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -6432,7 +6529,7 @@
         <v>238</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -6446,7 +6543,7 @@
         <v>248</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -6460,7 +6557,7 @@
         <v>248</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -6474,7 +6571,7 @@
         <v>248</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -6488,7 +6585,7 @@
         <v>256</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -6502,7 +6599,7 @@
         <v>256</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
@@ -6516,7 +6613,7 @@
         <v>256</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
@@ -6530,7 +6627,7 @@
         <v>269</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -6544,7 +6641,7 @@
         <v>269</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
@@ -6558,7 +6655,7 @@
         <v>269</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -6572,7 +6669,7 @@
         <v>279</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -6586,7 +6683,7 @@
         <v>279</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
@@ -6600,7 +6697,7 @@
         <v>279</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -6614,7 +6711,7 @@
         <v>287</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -6628,7 +6725,7 @@
         <v>287</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -6642,7 +6739,7 @@
         <v>287</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -6656,7 +6753,7 @@
         <v>297</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -6670,7 +6767,7 @@
         <v>297</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -6684,7 +6781,7 @@
         <v>297</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
@@ -6698,7 +6795,7 @@
         <v>308</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
@@ -6712,7 +6809,7 @@
         <v>308</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
@@ -6726,7 +6823,7 @@
         <v>308</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
@@ -6740,7 +6837,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
@@ -6754,7 +6851,7 @@
         <v>41</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
@@ -6768,7 +6865,7 @@
         <v>41</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -6782,7 +6879,7 @@
         <v>73</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
@@ -6796,7 +6893,7 @@
         <v>73</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D57" s="1">
         <v>2</v>
@@ -6810,7 +6907,7 @@
         <v>73</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
@@ -6824,7 +6921,7 @@
         <v>77</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -6838,7 +6935,7 @@
         <v>77</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D60" s="1">
         <v>2</v>
@@ -6852,7 +6949,7 @@
         <v>77</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -6866,7 +6963,7 @@
         <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -6880,7 +6977,7 @@
         <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D63" s="1">
         <v>2</v>
@@ -6894,7 +6991,7 @@
         <v>81</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D64" s="1">
         <v>3</v>
@@ -6908,7 +7005,7 @@
         <v>85</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -6922,7 +7019,7 @@
         <v>85</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D66" s="1">
         <v>2</v>
@@ -6936,7 +7033,7 @@
         <v>85</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
@@ -6950,7 +7047,7 @@
         <v>90</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
@@ -6964,7 +7061,7 @@
         <v>90</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D69" s="1">
         <v>2</v>
@@ -6978,7 +7075,7 @@
         <v>90</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D70" s="1">
         <v>3</v>
@@ -6992,7 +7089,7 @@
         <v>27</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -7006,7 +7103,7 @@
         <v>27</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
@@ -7020,7 +7117,7 @@
         <v>27</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="D73" s="1">
         <v>3</v>
@@ -7046,114 +7143,114 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
     </row>
   </sheetData>

--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="1030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2639" uniqueCount="1046">
   <si>
     <t>Id</t>
   </si>
@@ -2616,6 +2616,69 @@
     <t>/assets/maxseal/docs/2020 Automated Pricelist.pdf</t>
   </si>
   <si>
+    <t>d27</t>
+  </si>
+  <si>
+    <t>flo-tite-price-guide</t>
+  </si>
+  <si>
+    <t>Flo-Tite General Price Guide (Flo-Tite 2023 FINAL General Price Guide_12_20_2022 COMPRESSED.pdf)</t>
+  </si>
+  <si>
+    <t>Sep 2026</t>
+  </si>
+  <si>
+    <t>8.0 MB</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/Flo-Tite 2023 FINAL General Price Guide_12_20_2022 COMPRESSED.pdf</t>
+  </si>
+  <si>
+    <t>d28</t>
+  </si>
+  <si>
+    <t>tri-max-series-updated</t>
+  </si>
+  <si>
+    <t>Tri-Max Series Technical Bulletin — Updated (500-25-Max-Seal-HP-Butterfly-Valve-TB-2025-V25-final-new.pdf)</t>
+  </si>
+  <si>
+    <t>7.8 MB</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/500-25-Max-Seal-HP-Butterfly-Valve-TB-2025-V25-final-new.pdf</t>
+  </si>
+  <si>
+    <t>d29</t>
+  </si>
+  <si>
+    <t>hi-tek-series-alt</t>
+  </si>
+  <si>
+    <t>Hi-Tek Series Catalog — Alternate (502-24-HiTek-Double-Triple-Offsets_v01-COMPRESSED.pdf)</t>
+  </si>
+  <si>
+    <t>6.2 MB</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/502-24-HiTek-Double-Triple-Offsets_v01-COMPRESSED.pdf</t>
+  </si>
+  <si>
+    <t>d30</t>
+  </si>
+  <si>
+    <t>cryogenic-series-alt</t>
+  </si>
+  <si>
+    <t>Cryogenic Series Catalog — Alternate (154-23 CRYOGENIC BF Valve Catalog Low-temperature V100L200L_20220409_MAXSEAL R2 COMPRESSED (1).pdf)</t>
+  </si>
+  <si>
+    <t>11.0 MB</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/154-23 CRYOGENIC BF Valve Catalog Low-temperature V100L200L_20220409_MAXSEAL R2 COMPRESSED (1).pdf</t>
+  </si>
+  <si>
     <t>Effective</t>
   </si>
   <si>
@@ -2628,136 +2691,121 @@
     <t>Access</t>
   </si>
   <si>
-    <t>pl1</t>
+    <t>pl3</t>
+  </si>
+  <si>
+    <t>Published List Pricing Summary</t>
+  </si>
+  <si>
+    <t>2025.1</t>
+  </si>
+  <si>
+    <t>request</t>
+  </si>
+  <si>
+    <t>0.5 MB</t>
+  </si>
+  <si>
+    <t>pl4</t>
+  </si>
+  <si>
+    <t>Automated Pricelist (2020)</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>Jul 2023</t>
+  </si>
+  <si>
+    <t>download</t>
+  </si>
+  <si>
+    <t>3.2 MB</t>
+  </si>
+  <si>
+    <t>pl5</t>
+  </si>
+  <si>
+    <t>Flo-Tite General Price Guide (2023)</t>
+  </si>
+  <si>
+    <t>Dec 2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Aug 2026</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>FileType</t>
+  </si>
+  <si>
+    <t>CatalogDocSlug</t>
+  </si>
+  <si>
+    <t>ResType</t>
+  </si>
+  <si>
+    <t>Related</t>
+  </si>
+  <si>
+    <t>catalog</t>
+  </si>
+  <si>
+    <t>Product catalogs and technical datasheets by family.</t>
+  </si>
+  <si>
+    <t>Resilient Seated Butterfly Valves — Performance Series</t>
+  </si>
+  <si>
+    <t>Performance Series</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>4 pages</t>
+  </si>
+  <si>
+    <t>marketing</t>
+  </si>
+  <si>
+    <t>Marketing Resources</t>
+  </si>
+  <si>
+    <t>Brochures, presentations and approved brand assets.</t>
+  </si>
+  <si>
+    <t>Company Overview Brochure</t>
+  </si>
+  <si>
+    <t>Brochure</t>
+  </si>
+  <si>
+    <t>Company overview</t>
+  </si>
+  <si>
+    <t>pricelists</t>
+  </si>
+  <si>
+    <t>Price Lists</t>
+  </si>
+  <si>
+    <t>Current price lists for distributors and partners.</t>
   </si>
   <si>
     <t>Distributor Price List</t>
-  </si>
-  <si>
-    <t>2025.1</t>
-  </si>
-  <si>
-    <t>request</t>
-  </si>
-  <si>
-    <t>pl2</t>
-  </si>
-  <si>
-    <t>Resilient Seated Price List</t>
-  </si>
-  <si>
-    <t>pl3</t>
-  </si>
-  <si>
-    <t>Published List Pricing Summary</t>
-  </si>
-  <si>
-    <t>download</t>
-  </si>
-  <si>
-    <t>0.5 MB</t>
-  </si>
-  <si>
-    <t>pl4</t>
-  </si>
-  <si>
-    <t>Automated Pricelist (2020)</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>Jul 2023</t>
-  </si>
-  <si>
-    <t>3.2 MB</t>
-  </si>
-  <si>
-    <t>pl5</t>
-  </si>
-  <si>
-    <t>Flo-Tite General Price Guide (2023)</t>
-  </si>
-  <si>
-    <t>Dec 2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>Aug 2026</t>
-  </si>
-  <si>
-    <t>8.0 MB</t>
-  </si>
-  <si>
-    <t>/assets/maxseal/docs/Flo-Tite 2023 FINAL General Price Guide_12_20_2022 COMPRESSED.pdf</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>Family</t>
-  </si>
-  <si>
-    <t>FileType</t>
-  </si>
-  <si>
-    <t>CatalogDocSlug</t>
-  </si>
-  <si>
-    <t>ResType</t>
-  </si>
-  <si>
-    <t>Related</t>
-  </si>
-  <si>
-    <t>catalog</t>
-  </si>
-  <si>
-    <t>Product catalogs and technical datasheets by family.</t>
-  </si>
-  <si>
-    <t>Resilient Seated Butterfly Valves — Performance Series</t>
-  </si>
-  <si>
-    <t>Performance Series</t>
-  </si>
-  <si>
-    <t>PDF</t>
-  </si>
-  <si>
-    <t>4 pages</t>
-  </si>
-  <si>
-    <t>marketing</t>
-  </si>
-  <si>
-    <t>Marketing Resources</t>
-  </si>
-  <si>
-    <t>Brochures, presentations and approved brand assets.</t>
-  </si>
-  <si>
-    <t>Company Overview Brochure</t>
-  </si>
-  <si>
-    <t>Brochure</t>
-  </si>
-  <si>
-    <t>Company overview</t>
-  </si>
-  <si>
-    <t>pricelists</t>
-  </si>
-  <si>
-    <t>Price Lists</t>
-  </si>
-  <si>
-    <t>Current price lists for distributors and partners.</t>
   </si>
   <si>
     <t>Effective Jan 2025</t>
@@ -3596,7 +3644,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="8.01" style="1" customWidth="1"/>
@@ -4255,6 +4303,146 @@
         <v>858</v>
       </c>
     </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -4266,7 +4454,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="8.01" style="1" customWidth="1"/>
@@ -4289,16 +4477,16 @@
         <v>436</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>859</v>
+        <v>880</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>861</v>
+        <v>882</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>725</v>
@@ -4309,10 +4497,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>777</v>
@@ -4321,126 +4509,74 @@
         <v>759</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>867</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>866</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>869</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="C4" s="6" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>751</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="I3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="I5" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="I6" t="s">
-        <v>884</v>
+      <c r="D4" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="I4" t="s">
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -4479,63 +4615,63 @@
         <v>438</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>888</v>
+        <v>903</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>726</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>889</v>
+        <v>904</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>724</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>859</v>
+        <v>880</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>730</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>893</v>
+        <v>908</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>895</v>
+        <v>910</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>32</v>
@@ -4543,22 +4679,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>739</v>
@@ -4566,25 +4702,25 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>904</v>
+        <v>919</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>864</v>
+        <v>922</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>907</v>
+        <v>923</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>908</v>
+        <v>924</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>909</v>
+        <v>925</v>
       </c>
     </row>
   </sheetData>
@@ -4611,7 +4747,7 @@
         <v>436</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>910</v>
+        <v>926</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -5531,45 +5667,45 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>912</v>
+        <v>928</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>913</v>
+        <v>929</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>915</v>
+        <v>931</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>916</v>
+        <v>932</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>917</v>
+        <v>933</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>918</v>
+        <v>934</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>920</v>
+        <v>936</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>921</v>
+        <v>937</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>922</v>
+        <v>938</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>121</v>
@@ -5577,22 +5713,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>923</v>
+        <v>939</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>924</v>
+        <v>940</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>925</v>
+        <v>941</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>922</v>
+        <v>938</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>138</v>
@@ -5600,22 +5736,22 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>927</v>
+        <v>943</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>928</v>
+        <v>944</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>929</v>
+        <v>945</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>922</v>
+        <v>938</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>151</v>
@@ -5623,22 +5759,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>930</v>
+        <v>946</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>931</v>
+        <v>947</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>932</v>
+        <v>948</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>933</v>
+        <v>949</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>922</v>
+        <v>938</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>161</v>
@@ -5646,22 +5782,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>934</v>
+        <v>950</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>935</v>
+        <v>951</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>936</v>
+        <v>952</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>922</v>
+        <v>938</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>174</v>
@@ -5669,22 +5805,22 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>937</v>
+        <v>953</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>954</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>938</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>939</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>940</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>922</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>188</v>
@@ -5692,22 +5828,22 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>941</v>
+        <v>957</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>942</v>
+        <v>958</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>943</v>
+        <v>959</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>944</v>
+        <v>960</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>922</v>
+        <v>938</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>197</v>
@@ -5715,22 +5851,22 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>945</v>
+        <v>961</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>946</v>
+        <v>962</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>635</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>947</v>
+        <v>963</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>633</v>
@@ -5738,22 +5874,22 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>949</v>
+        <v>965</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>950</v>
+        <v>966</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>639</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>951</v>
+        <v>967</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>637</v>
@@ -5761,22 +5897,22 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>952</v>
+        <v>968</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>953</v>
+        <v>969</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>643</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>641</v>
@@ -5784,22 +5920,22 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>956</v>
+        <v>972</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>647</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>957</v>
+        <v>973</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>645</v>
@@ -5807,22 +5943,22 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>958</v>
+        <v>974</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>959</v>
+        <v>975</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>651</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>960</v>
+        <v>976</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>649</v>
@@ -5830,22 +5966,22 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>961</v>
+        <v>977</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>655</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>963</v>
+        <v>979</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>653</v>
@@ -5853,22 +5989,22 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>964</v>
+        <v>980</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>965</v>
+        <v>981</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>659</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>966</v>
+        <v>982</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>657</v>
@@ -5876,22 +6012,22 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>663</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>969</v>
+        <v>985</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>661</v>
@@ -5899,22 +6035,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>971</v>
+        <v>987</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>667</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>972</v>
+        <v>988</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>665</v>
@@ -5922,22 +6058,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>973</v>
+        <v>989</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>671</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>975</v>
+        <v>991</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>669</v>
@@ -5945,22 +6081,22 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>976</v>
+        <v>992</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>675</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>978</v>
+        <v>994</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>673</v>
@@ -5968,22 +6104,22 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>979</v>
+        <v>995</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>679</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>677</v>
@@ -5991,22 +6127,22 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>982</v>
+        <v>998</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>983</v>
+        <v>999</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>683</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>984</v>
+        <v>1000</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>681</v>
@@ -6014,45 +6150,45 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>985</v>
+        <v>1001</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>986</v>
+        <v>1002</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>987</v>
+        <v>1003</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>988</v>
+        <v>1004</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>989</v>
+        <v>1005</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>990</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>991</v>
+        <v>1007</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>992</v>
+        <v>1008</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>993</v>
+        <v>1009</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>735</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>994</v>
+        <v>1010</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>995</v>
+        <v>1011</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>729</v>
@@ -6060,22 +6196,22 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>996</v>
+        <v>1012</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>997</v>
+        <v>1013</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>736</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>998</v>
+        <v>1014</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>995</v>
+        <v>1011</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>729</v>
@@ -6123,7 +6259,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6137,7 +6273,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -6151,7 +6287,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -6165,7 +6301,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -6179,7 +6315,7 @@
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -6193,7 +6329,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -6207,7 +6343,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -6221,7 +6357,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -6235,7 +6371,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -6249,7 +6385,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -6263,7 +6399,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -6277,7 +6413,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -6291,7 +6427,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -6305,7 +6441,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -6319,7 +6455,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -6333,7 +6469,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -6347,7 +6483,7 @@
         <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -6361,7 +6497,7 @@
         <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -6375,7 +6511,7 @@
         <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -6389,7 +6525,7 @@
         <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -6403,7 +6539,7 @@
         <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -6417,7 +6553,7 @@
         <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -6431,7 +6567,7 @@
         <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
@@ -6445,7 +6581,7 @@
         <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -6459,7 +6595,7 @@
         <v>228</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -6473,7 +6609,7 @@
         <v>228</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -6487,7 +6623,7 @@
         <v>228</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -6501,7 +6637,7 @@
         <v>238</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -6515,7 +6651,7 @@
         <v>238</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -6529,7 +6665,7 @@
         <v>238</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -6543,7 +6679,7 @@
         <v>248</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -6557,7 +6693,7 @@
         <v>248</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -6571,7 +6707,7 @@
         <v>248</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -6585,7 +6721,7 @@
         <v>256</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -6599,7 +6735,7 @@
         <v>256</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
@@ -6613,7 +6749,7 @@
         <v>256</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
@@ -6627,7 +6763,7 @@
         <v>269</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -6641,7 +6777,7 @@
         <v>269</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
@@ -6655,7 +6791,7 @@
         <v>269</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -6669,7 +6805,7 @@
         <v>279</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -6683,7 +6819,7 @@
         <v>279</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
@@ -6697,7 +6833,7 @@
         <v>279</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -6711,7 +6847,7 @@
         <v>287</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -6725,7 +6861,7 @@
         <v>287</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -6739,7 +6875,7 @@
         <v>287</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -6753,7 +6889,7 @@
         <v>297</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -6767,7 +6903,7 @@
         <v>297</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -6781,7 +6917,7 @@
         <v>297</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
@@ -6795,7 +6931,7 @@
         <v>308</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
@@ -6809,7 +6945,7 @@
         <v>308</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
@@ -6823,7 +6959,7 @@
         <v>308</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
@@ -6837,7 +6973,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
@@ -6851,7 +6987,7 @@
         <v>41</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
@@ -6865,7 +7001,7 @@
         <v>41</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -6879,7 +7015,7 @@
         <v>73</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
@@ -6893,7 +7029,7 @@
         <v>73</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D57" s="1">
         <v>2</v>
@@ -6907,7 +7043,7 @@
         <v>73</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
@@ -6921,7 +7057,7 @@
         <v>77</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -6935,7 +7071,7 @@
         <v>77</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D60" s="1">
         <v>2</v>
@@ -6949,7 +7085,7 @@
         <v>77</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -6963,7 +7099,7 @@
         <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -6977,7 +7113,7 @@
         <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D63" s="1">
         <v>2</v>
@@ -6991,7 +7127,7 @@
         <v>81</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D64" s="1">
         <v>3</v>
@@ -7005,7 +7141,7 @@
         <v>85</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -7019,7 +7155,7 @@
         <v>85</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D66" s="1">
         <v>2</v>
@@ -7033,7 +7169,7 @@
         <v>85</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
@@ -7047,7 +7183,7 @@
         <v>90</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
@@ -7061,7 +7197,7 @@
         <v>90</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D69" s="1">
         <v>2</v>
@@ -7075,7 +7211,7 @@
         <v>90</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D70" s="1">
         <v>3</v>
@@ -7089,7 +7225,7 @@
         <v>27</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -7103,7 +7239,7 @@
         <v>27</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
@@ -7117,7 +7253,7 @@
         <v>27</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="D73" s="1">
         <v>3</v>
@@ -7143,114 +7279,114 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1002</v>
+        <v>1018</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1003</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1004</v>
+        <v>1020</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1005</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1006</v>
+        <v>1022</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1007</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1009</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1010</v>
+        <v>1026</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1011</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1013</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1014</v>
+        <v>1030</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1015</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1016</v>
+        <v>1032</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1017</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1018</v>
+        <v>1034</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1019</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1020</v>
+        <v>1036</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1021</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1022</v>
+        <v>1038</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1023</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1024</v>
+        <v>1040</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1025</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1026</v>
+        <v>1042</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1027</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1028</v>
+        <v>1044</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1029</v>
+        <v>1045</v>
       </c>
     </row>
   </sheetData>

--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2639" uniqueCount="1046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2662" uniqueCount="1043">
   <si>
     <t>Id</t>
   </si>
@@ -2226,6 +2226,9 @@
     <t>CoverAssetPath</t>
   </si>
   <si>
+    <t>ShowInCatalog</t>
+  </si>
+  <si>
     <t>d1</t>
   </si>
   <si>
@@ -2250,6 +2253,9 @@
     <t>/assets/maxseal/docs/resilient-seated-catalog-cover.png</t>
   </si>
   <si>
+    <t>FALSE</t>
+  </si>
+  <si>
     <t>d2</t>
   </si>
   <si>
@@ -2689,21 +2695,6 @@
   </si>
   <si>
     <t>Access</t>
-  </si>
-  <si>
-    <t>pl3</t>
-  </si>
-  <si>
-    <t>Published List Pricing Summary</t>
-  </si>
-  <si>
-    <t>2025.1</t>
-  </si>
-  <si>
-    <t>request</t>
-  </si>
-  <si>
-    <t>0.5 MB</t>
   </si>
   <si>
     <t>pl4</t>
@@ -3181,7 +3172,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -3226,8 +3217,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3244,6 +3238,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -3274,7 +3273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
@@ -3312,6 +3311,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3644,7 +3644,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="8.01" style="1" customWidth="1"/>
@@ -3656,9 +3656,10 @@
     <col min="7" max="8" width="12.01" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.01" style="1" customWidth="1"/>
     <col min="10" max="11" width="44.01" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3692,517 +3693,583 @@
       <c r="K1" s="4" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="13" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>221</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>689</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>737</v>
+      </c>
+      <c r="L2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+      <c r="L3" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>138</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+      <c r="L4" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>161</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+      <c r="L5" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>763</v>
+      </c>
+      <c r="L6" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>174</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+      <c r="L7" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="I9" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="L9" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>782</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>777</v>
-      </c>
       <c r="G10" s="6" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>787</v>
+      </c>
+      <c r="L10" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>161</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>793</v>
+      </c>
+      <c r="L11" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>221</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>797</v>
+      </c>
+      <c r="L12" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>231</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>801</v>
+      </c>
+      <c r="L13" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>249</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>805</v>
+      </c>
+      <c r="L14" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>188</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>809</v>
+      </c>
+      <c r="L15" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>262</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>813</v>
+      </c>
+      <c r="L16" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>272</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>817</v>
+      </c>
+      <c r="L17" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>280</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>821</v>
+      </c>
+      <c r="L18" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>290</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+      <c r="L19" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>301</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>829</v>
+      </c>
+      <c r="L20" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>310</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>833</v>
+      </c>
+      <c r="L21" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>241</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>837</v>
+      </c>
+      <c r="L22" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>197</v>
@@ -4211,145 +4278,163 @@
         <v>322</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+      <c r="L23" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>209</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+      <c r="L24" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>345</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>850</v>
+      </c>
+      <c r="L25" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>855</v>
+      </c>
+      <c r="L26" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>416</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>860</v>
+      </c>
+      <c r="L27" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>100</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>100</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>272</v>
@@ -4358,33 +4443,36 @@
         <v>100</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>100</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>280</v>
@@ -4393,33 +4481,36 @@
         <v>100</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>100</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>310</v>
@@ -4428,19 +4519,22 @@
         <v>100</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>100</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>100</v>
+      </c>
+      <c r="L31" t="s">
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -4454,7 +4548,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="8.01" style="1" customWidth="1"/>
@@ -4477,16 +4571,16 @@
         <v>436</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>725</v>
@@ -4495,88 +4589,62 @@
         <v>727</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>884</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>885</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="6" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>751</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="B2" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="C2" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>888</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="I2" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>891</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>891</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>893</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>894</v>
+        <v>865</v>
       </c>
       <c r="I3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>898</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>893</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="I4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
   </sheetData>
@@ -4615,63 +4683,63 @@
         <v>438</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>900</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>901</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>902</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>903</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>726</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>724</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>730</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>909</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>910</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>912</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>32</v>
@@ -4679,48 +4747,48 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>913</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>916</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>917</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>918</v>
-      </c>
       <c r="K3" s="6" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>920</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>921</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>922</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>924</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>925</v>
       </c>
     </row>
   </sheetData>
@@ -4747,7 +4815,7 @@
         <v>436</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -5667,45 +5735,45 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>928</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>930</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>931</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>932</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>121</v>
@@ -5713,22 +5781,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>138</v>
@@ -5736,22 +5804,22 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>942</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>935</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>943</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>944</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>945</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>938</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>151</v>
@@ -5759,22 +5827,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>946</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>935</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>947</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>948</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>949</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>938</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>161</v>
@@ -5782,22 +5850,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>174</v>
@@ -5805,22 +5873,22 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>935</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>954</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>955</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>956</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>938</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>188</v>
@@ -5828,22 +5896,22 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>954</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>957</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>935</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>958</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>960</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>938</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>197</v>
@@ -5851,22 +5919,22 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>635</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>633</v>
@@ -5874,22 +5942,22 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>639</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>637</v>
@@ -5897,22 +5965,22 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>643</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>641</v>
@@ -5920,22 +5988,22 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>647</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>645</v>
@@ -5943,22 +6011,22 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>651</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>649</v>
@@ -5966,22 +6034,22 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>655</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>653</v>
@@ -5989,22 +6057,22 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>659</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>657</v>
@@ -6012,22 +6080,22 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>663</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>661</v>
@@ -6035,22 +6103,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>667</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>665</v>
@@ -6058,22 +6126,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>671</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>669</v>
@@ -6081,22 +6149,22 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>675</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>673</v>
@@ -6104,22 +6172,22 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>679</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>677</v>
@@ -6127,22 +6195,22 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>683</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>681</v>
@@ -6150,71 +6218,71 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>1001</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>935</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="F22" s="6" t="s">
         <v>1002</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>1003</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>1008</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>1011</v>
-      </c>
       <c r="G23" s="6" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -6259,7 +6327,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6273,7 +6341,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -6287,7 +6355,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -6301,7 +6369,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -6315,7 +6383,7 @@
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -6329,7 +6397,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -6343,7 +6411,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -6357,7 +6425,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -6371,7 +6439,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -6385,7 +6453,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -6399,7 +6467,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -6413,7 +6481,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -6427,7 +6495,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -6441,7 +6509,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -6455,7 +6523,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -6469,7 +6537,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -6483,7 +6551,7 @@
         <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -6497,7 +6565,7 @@
         <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -6511,7 +6579,7 @@
         <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -6525,7 +6593,7 @@
         <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -6539,7 +6607,7 @@
         <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -6553,7 +6621,7 @@
         <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -6567,7 +6635,7 @@
         <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
@@ -6581,7 +6649,7 @@
         <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -6595,7 +6663,7 @@
         <v>228</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -6609,7 +6677,7 @@
         <v>228</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -6623,7 +6691,7 @@
         <v>228</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -6637,7 +6705,7 @@
         <v>238</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -6651,7 +6719,7 @@
         <v>238</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -6665,7 +6733,7 @@
         <v>238</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -6679,7 +6747,7 @@
         <v>248</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -6693,7 +6761,7 @@
         <v>248</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -6707,7 +6775,7 @@
         <v>248</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -6721,7 +6789,7 @@
         <v>256</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -6735,7 +6803,7 @@
         <v>256</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
@@ -6749,7 +6817,7 @@
         <v>256</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
@@ -6763,7 +6831,7 @@
         <v>269</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -6777,7 +6845,7 @@
         <v>269</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
@@ -6791,7 +6859,7 @@
         <v>269</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -6805,7 +6873,7 @@
         <v>279</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -6819,7 +6887,7 @@
         <v>279</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
@@ -6833,7 +6901,7 @@
         <v>279</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -6847,7 +6915,7 @@
         <v>287</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -6861,7 +6929,7 @@
         <v>287</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -6875,7 +6943,7 @@
         <v>287</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -6889,7 +6957,7 @@
         <v>297</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -6903,7 +6971,7 @@
         <v>297</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -6917,7 +6985,7 @@
         <v>297</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
@@ -6931,7 +6999,7 @@
         <v>308</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
@@ -6945,7 +7013,7 @@
         <v>308</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
@@ -6959,7 +7027,7 @@
         <v>308</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
@@ -6973,7 +7041,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
@@ -6987,7 +7055,7 @@
         <v>41</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
@@ -7001,7 +7069,7 @@
         <v>41</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -7015,7 +7083,7 @@
         <v>73</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
@@ -7029,7 +7097,7 @@
         <v>73</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D57" s="1">
         <v>2</v>
@@ -7043,7 +7111,7 @@
         <v>73</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
@@ -7057,7 +7125,7 @@
         <v>77</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -7071,7 +7139,7 @@
         <v>77</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D60" s="1">
         <v>2</v>
@@ -7085,7 +7153,7 @@
         <v>77</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -7099,7 +7167,7 @@
         <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -7113,7 +7181,7 @@
         <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D63" s="1">
         <v>2</v>
@@ -7127,7 +7195,7 @@
         <v>81</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D64" s="1">
         <v>3</v>
@@ -7141,7 +7209,7 @@
         <v>85</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -7155,7 +7223,7 @@
         <v>85</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D66" s="1">
         <v>2</v>
@@ -7169,7 +7237,7 @@
         <v>85</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
@@ -7183,7 +7251,7 @@
         <v>90</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
@@ -7197,7 +7265,7 @@
         <v>90</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D69" s="1">
         <v>2</v>
@@ -7211,7 +7279,7 @@
         <v>90</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D70" s="1">
         <v>3</v>
@@ -7225,7 +7293,7 @@
         <v>27</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -7239,7 +7307,7 @@
         <v>27</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
@@ -7253,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D73" s="1">
         <v>3</v>
@@ -7279,114 +7347,114 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
     </row>
   </sheetData>
